--- a/results/experiment2_moa_vs_frameworks_same_time/summaries/experiment2_moa_vs_frameworks_same_time_summary.xlsx
+++ b/results/experiment2_moa_vs_frameworks_same_time/summaries/experiment2_moa_vs_frameworks_same_time_summary.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>exp2: MOA-NSGAII vs CMOEMT, TriP, ARACMO under the same time budget; LERD excluded; empty Pareto fronts excluded; compare HV and IGD</t>
+          <t>exp2: MOA-NSGAII vs CMOEMT, TriP, ARACMO under the same time budget; empty Pareto fronts excluded; compare HV and IGD</t>
         </is>
       </c>
     </row>
@@ -612,11 +612,7 @@
           <t>excluded_methods</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>LERD</t>
-        </is>
-      </c>
+      <c r="B4" s="2" t="inlineStr"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -626,7 +622,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>normalized HV using per-product min/max over CMOEMT, TriP, ARACMO, and MOA-NSGAII Pareto fronts only; LERD excluded; empty fronts excluded; expanded by 10% on both sides</t>
+          <t>normalized HV using per-product min/max over CMOEMT, TriP, ARACMO, and MOA-NSGAII Pareto fronts only; empty fronts excluded; expanded by 10% on both sides</t>
         </is>
       </c>
     </row>
@@ -638,7 +634,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>per-product nondominated union of CMOEMT, TriP, ARACMO, and MOA-NSGAII final fronts only; LERD excluded; empty fronts excluded; normalized by PRODUCT_HV_BOXES</t>
+          <t>per-product nondominated union of CMOEMT, TriP, ARACMO, and MOA-NSGAII final fronts only; empty fronts excluded; normalized by PRODUCT_HV_BOXES</t>
         </is>
       </c>
     </row>
@@ -674,7 +670,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Experiment-2 HV/IGD uses its own no-LERD framework comparison reference. HV values are not directly comparable with Experiment 1 unless the same ideal/ref are used.</t>
+          <t>Experiment-2 HV/IGD uses its own no-framework comparison reference. HV values are not directly comparable with Experiment 1 unless the same ideal/ref are used.</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1041,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>HV(mean(std)) and runtime(average), LERD excluded</t>
+          <t>HV(mean(std)) and runtime(average), excluded</t>
         </is>
       </c>
       <c r="B1" s="12" t="n"/>
@@ -1716,7 +1712,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>IGD(mean(std)) and runtime(average), LERD excluded</t>
+          <t>IGD(mean(std)) and runtime(average), excluded</t>
         </is>
       </c>
       <c r="B1" s="3" t="n"/>
